--- a/content/assets/book-library.xlsx
+++ b/content/assets/book-library.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fabian\OneDrive\Desktop\book_lore\content\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1bf321a538ee898/Desktop/book_lore/content/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB5D161-00E4-46F5-A7E3-FB7DE1440939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{5FB5D161-00E4-46F5-A7E3-FB7DE1440939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE081DF-93EA-4807-AF50-7C3ABF588AF0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,28 +25,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Gustav</t>
-  </si>
-  <si>
-    <t>Pierre</t>
-  </si>
-  <si>
-    <t>Adel</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Ereen</t>
+  </si>
+  <si>
+    <r>
+      <t>[[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>regionen/ereen/arden/index|Arden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]]</t>
+    </r>
+  </si>
+  <si>
+    <t>Cazarad</t>
+  </si>
+  <si>
+    <r>
+      <t>[[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>regionen/ereen/cazarad/index|Cazarad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]]</t>
+    </r>
+  </si>
+  <si>
+    <t>Arden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanrim </t>
+  </si>
+  <si>
+    <r>
+      <t>[[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>regionen/ereen/vanrim/index|Vanrim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>regionen/ereen/index|Ereen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -69,8 +176,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -353,36 +463,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="64.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B13">
-    <sortCondition ref="A1:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B5">
+    <sortCondition ref="A1:A5"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
